--- a/Configs/GameConfig/Datas/fg/#StartLayout-开局布局.xlsx
+++ b/Configs/GameConfig/Datas/fg/#StartLayout-开局布局.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>clearance</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ownerAnchor</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +524,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -569,6 +579,11 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>净空半径(米),不重叠自检用</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>出口所属建筑的锚点ID:出口随该建筑旋转 / 搬迁(FG3-LOG-01);其它行填none</t>
         </is>
       </c>
     </row>
@@ -609,6 +624,11 @@
       <c r="J4" t="n">
         <v>4</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -647,6 +667,11 @@
       <c r="J5" t="n">
         <v>3</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -685,6 +710,11 @@
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -723,6 +753,11 @@
       <c r="J7" t="n">
         <v>3</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -761,6 +796,11 @@
       <c r="J8" t="n">
         <v>3.5</v>
       </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -799,6 +839,11 @@
       <c r="J9" t="n">
         <v>3</v>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -837,6 +882,11 @@
       <c r="J10" t="n">
         <v>3</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -875,6 +925,11 @@
       <c r="J11" t="n">
         <v>3</v>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -913,6 +968,11 @@
       <c r="J12" t="n">
         <v>3</v>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -951,6 +1011,11 @@
       <c r="J13" t="n">
         <v>1.5</v>
       </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>warehouse</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr"/>
@@ -989,6 +1054,11 @@
       <c r="J14" t="n">
         <v>1.5</v>
       </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>assembly_station</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr"/>
@@ -1027,6 +1097,11 @@
       <c r="J15" t="n">
         <v>1.5</v>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr"/>
@@ -1065,6 +1140,11 @@
       <c r="J16" t="n">
         <v>1.5</v>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr"/>
@@ -1103,6 +1183,11 @@
       <c r="J17" t="n">
         <v>2</v>
       </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
@@ -1141,6 +1226,11 @@
       <c r="J18" t="n">
         <v>2</v>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
@@ -1179,6 +1269,11 @@
       <c r="J19" t="n">
         <v>2</v>
       </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
@@ -1216,6 +1311,11 @@
       </c>
       <c r="J20" t="n">
         <v>0.5</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#StartLayout-开局布局.xlsx
+++ b/Configs/GameConfig/Datas/fg/#StartLayout-开局布局.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="J4" t="n">
         <v>4</v>
